--- a/data/trans_orig/IP09-Clase-trans_orig.xlsx
+++ b/data/trans_orig/IP09-Clase-trans_orig.xlsx
@@ -738,7 +738,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>3440</t>
+          <t>4006</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -753,7 +753,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>35,15%</t>
+          <t>40,93%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1281</t>
+          <t>1258</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>6015</t>
+          <t>5936</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>11,16%</t>
+          <t>10,97%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>52,43%</t>
+          <t>51,73%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1978</t>
+          <t>1990</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>8299</t>
+          <t>8214</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>9,3%</t>
+          <t>9,36%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>39,03%</t>
+          <t>38,63%</t>
         </is>
       </c>
     </row>
@@ -846,7 +846,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>6349</t>
+          <t>5783</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -861,7 +861,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>64,85%</t>
+          <t>59,07%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>5459</t>
+          <t>5538</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>10193</t>
+          <t>10216</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>47,57%</t>
+          <t>48,27%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>88,84%</t>
+          <t>89,03%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>12965</t>
+          <t>13050</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>19286</t>
+          <t>19274</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>60,97%</t>
+          <t>61,37%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>90,7%</t>
+          <t>90,64%</t>
         </is>
       </c>
     </row>
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>832</t>
+          <t>1299</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>5538</t>
+          <t>5507</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>9,57%</t>
+          <t>14,95%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>63,75%</t>
+          <t>63,39%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>708</t>
+          <t>731</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>5869</t>
+          <t>6367</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>4,32%</t>
+          <t>4,46%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>35,8%</t>
+          <t>38,84%</t>
         </is>
       </c>
     </row>
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>3149</t>
+          <t>3180</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>7855</t>
+          <t>7388</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>36,25%</t>
+          <t>36,61%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>90,43%</t>
+          <t>85,05%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>10523</t>
+          <t>10025</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>15684</t>
+          <t>15661</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>64,2%</t>
+          <t>61,16%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>95,68%</t>
+          <t>95,54%</t>
         </is>
       </c>
     </row>
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1938</t>
+          <t>1860</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>7384</t>
+          <t>6872</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>13,97%</t>
+          <t>13,41%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>53,23%</t>
+          <t>49,54%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1948</t>
+          <t>1955</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>7530</t>
+          <t>7576</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>10,99%</t>
+          <t>11,03%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>42,51%</t>
+          <t>42,77%</t>
         </is>
       </c>
     </row>
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>6487</t>
+          <t>6999</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>11933</t>
+          <t>12011</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>46,77%</t>
+          <t>50,46%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>86,03%</t>
+          <t>86,59%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>10184</t>
+          <t>10138</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>15766</t>
+          <t>15759</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>57,49%</t>
+          <t>57,23%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>89,01%</t>
+          <t>88,97%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2407</t>
+          <t>2431</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>8053</t>
+          <t>8577</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>13,83%</t>
+          <t>13,97%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>46,25%</t>
+          <t>49,26%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1994</t>
+          <t>1990</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>8123</t>
+          <t>8110</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>9,96%</t>
+          <t>9,94%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>40,56%</t>
+          <t>40,5%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>5725</t>
+          <t>5845</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>14272</t>
+          <t>14314</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>15,29%</t>
+          <t>15,62%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>38,13%</t>
+          <t>38,24%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>9357</t>
+          <t>8833</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>15003</t>
+          <t>14979</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>53,75%</t>
+          <t>50,74%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>86,17%</t>
+          <t>86,03%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>11901</t>
+          <t>11914</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>18030</t>
+          <t>18034</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>59,44%</t>
+          <t>59,5%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>90,04%</t>
+          <t>90,06%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>23162</t>
+          <t>23120</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>31709</t>
+          <t>31589</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>61,87%</t>
+          <t>61,76%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>84,71%</t>
+          <t>84,38%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>588</t>
+          <t>619</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>4551</t>
+          <t>4770</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>6,72%</t>
+          <t>7,08%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>52,02%</t>
+          <t>54,52%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>2721</t>
+          <t>2647</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>8824</t>
+          <t>8716</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>16,82%</t>
+          <t>16,36%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>54,53%</t>
+          <t>53,87%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>4070</t>
+          <t>4093</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>11380</t>
+          <t>11009</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>16,33%</t>
+          <t>16,42%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>45,65%</t>
+          <t>44,16%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>4198</t>
+          <t>3979</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>8161</t>
+          <t>8130</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>47,98%</t>
+          <t>45,48%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>93,28%</t>
+          <t>92,92%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>7357</t>
+          <t>7465</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>13460</t>
+          <t>13534</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>45,47%</t>
+          <t>46,13%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>83,18%</t>
+          <t>83,64%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>13551</t>
+          <t>13922</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>20861</t>
+          <t>20838</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>54,35%</t>
+          <t>55,84%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>83,67%</t>
+          <t>83,58%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>669</t>
+          <t>647</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>4618</t>
+          <t>4562</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>12,64%</t>
+          <t>12,21%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>87,21%</t>
+          <t>86,16%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>1276</t>
+          <t>1246</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>5856</t>
+          <t>5663</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>16,1%</t>
+          <t>15,72%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>73,9%</t>
+          <t>71,46%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>2905</t>
+          <t>2709</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>9012</t>
+          <t>8864</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>21,97%</t>
+          <t>20,49%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>68,17%</t>
+          <t>67,05%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>677</t>
+          <t>733</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>4626</t>
+          <t>4648</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>12,79%</t>
+          <t>13,84%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>87,36%</t>
+          <t>87,79%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>2068</t>
+          <t>2261</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>6648</t>
+          <t>6678</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>26,1%</t>
+          <t>28,54%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>83,9%</t>
+          <t>84,28%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>4208</t>
+          <t>4356</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>10315</t>
+          <t>10511</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>31,83%</t>
+          <t>32,95%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>78,03%</t>
+          <t>79,51%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>6544</t>
+          <t>6668</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>15609</t>
+          <t>16065</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>12,4%</t>
+          <t>12,63%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>29,57%</t>
+          <t>30,43%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>17578</t>
+          <t>17439</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>30173</t>
+          <t>29805</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>22,49%</t>
+          <t>22,31%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>38,6%</t>
+          <t>38,13%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>26574</t>
+          <t>26567</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>41974</t>
+          <t>42528</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2881,7 +2881,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>32,05%</t>
+          <t>32,48%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>37181</t>
+          <t>36725</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>46246</t>
+          <t>46122</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>70,43%</t>
+          <t>69,57%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>87,6%</t>
+          <t>87,37%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>47991</t>
+          <t>48359</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>60586</t>
+          <t>60725</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>61,4%</t>
+          <t>61,87%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>77,51%</t>
+          <t>77,69%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>88979</t>
+          <t>88425</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>104379</t>
+          <t>104386</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,7 +2989,7 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>67,95%</t>
+          <t>67,52%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
@@ -3368,12 +3368,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>657</t>
+          <t>662</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>4307</t>
+          <t>4603</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3383,12 +3383,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>9,66%</t>
+          <t>9,73%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>63,32%</t>
+          <t>67,68%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3408,7 +3408,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>4050</t>
+          <t>3568</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3423,7 +3423,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>54,04%</t>
+          <t>47,62%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3438,12 +3438,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1393</t>
+          <t>1389</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>7000</t>
+          <t>6848</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3453,12 +3453,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>9,74%</t>
+          <t>9,72%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>48,96%</t>
+          <t>47,9%</t>
         </is>
       </c>
     </row>
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2495</t>
+          <t>2199</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>6145</t>
+          <t>6140</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3496,12 +3496,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>36,68%</t>
+          <t>32,32%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>90,34%</t>
+          <t>90,27%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3516,7 +3516,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>3444</t>
+          <t>3926</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -3531,7 +3531,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>45,96%</t>
+          <t>52,38%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -3551,12 +3551,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>7296</t>
+          <t>7448</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>12903</t>
+          <t>12907</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3566,12 +3566,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>51,04%</t>
+          <t>52,1%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>90,26%</t>
+          <t>90,28%</t>
         </is>
       </c>
     </row>
@@ -3711,12 +3711,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>576</t>
+          <t>574</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>4455</t>
+          <t>4424</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3726,12 +3726,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>6,8%</t>
+          <t>6,78%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>52,56%</t>
+          <t>52,2%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3751,7 +3751,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>3004</t>
+          <t>3394</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3766,7 +3766,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>36,17%</t>
+          <t>40,87%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3781,12 +3781,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>692</t>
+          <t>684</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>5721</t>
+          <t>5859</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3796,12 +3796,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>4,12%</t>
+          <t>4,08%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>34,1%</t>
+          <t>34,92%</t>
         </is>
       </c>
     </row>
@@ -3824,12 +3824,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>4020</t>
+          <t>4051</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>7899</t>
+          <t>7901</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3839,12 +3839,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>47,44%</t>
+          <t>47,8%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>93,2%</t>
+          <t>93,22%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3859,7 +3859,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>5301</t>
+          <t>4911</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -3874,7 +3874,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>63,83%</t>
+          <t>59,13%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -3894,12 +3894,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>11059</t>
+          <t>10921</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>16088</t>
+          <t>16096</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3909,12 +3909,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>65,9%</t>
+          <t>65,08%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>95,88%</t>
+          <t>95,92%</t>
         </is>
       </c>
     </row>
@@ -4054,12 +4054,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>630</t>
+          <t>576</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>4717</t>
+          <t>4705</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4069,12 +4069,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>7,69%</t>
+          <t>7,03%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>57,65%</t>
+          <t>57,5%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4094,7 +4094,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>3221</t>
+          <t>2549</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4109,7 +4109,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>26,52%</t>
+          <t>20,99%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4124,12 +4124,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>644</t>
+          <t>650</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>5814</t>
+          <t>6028</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4139,12 +4139,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>3,2%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>28,6%</t>
+          <t>29,65%</t>
         </is>
       </c>
     </row>
@@ -4167,12 +4167,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>3465</t>
+          <t>3477</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>7552</t>
+          <t>7606</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4182,12 +4182,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>42,35%</t>
+          <t>42,5%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>92,31%</t>
+          <t>92,97%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4202,7 +4202,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>8924</t>
+          <t>9596</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -4217,7 +4217,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>73,48%</t>
+          <t>79,01%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -4237,12 +4237,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>14513</t>
+          <t>14299</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>19683</t>
+          <t>19677</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4252,12 +4252,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>71,4%</t>
+          <t>70,35%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>96,83%</t>
+          <t>96,8%</t>
         </is>
       </c>
     </row>
@@ -4397,12 +4397,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>7396</t>
+          <t>7971</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>16837</t>
+          <t>16561</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4412,12 +4412,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>21,47%</t>
+          <t>23,13%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>48,87%</t>
+          <t>48,06%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4432,12 +4432,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>13376</t>
+          <t>13079</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>24298</t>
+          <t>23613</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4447,12 +4447,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>34,29%</t>
+          <t>33,52%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>62,28%</t>
+          <t>60,53%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4467,12 +4467,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>23141</t>
+          <t>23959</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>37997</t>
+          <t>37601</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4482,12 +4482,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>31,5%</t>
+          <t>32,61%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>51,72%</t>
+          <t>51,18%</t>
         </is>
       </c>
     </row>
@@ -4510,12 +4510,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>17618</t>
+          <t>17894</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>27059</t>
+          <t>26484</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4525,12 +4525,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>51,13%</t>
+          <t>51,94%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>78,53%</t>
+          <t>76,87%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4545,12 +4545,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>14714</t>
+          <t>15399</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>25636</t>
+          <t>25933</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>37,72%</t>
+          <t>39,47%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>65,71%</t>
+          <t>66,48%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4580,12 +4580,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>35470</t>
+          <t>35866</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>50326</t>
+          <t>49508</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4595,12 +4595,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>48,28%</t>
+          <t>48,82%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>68,5%</t>
+          <t>67,39%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>4012</t>
+          <t>3685</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>10622</t>
+          <t>10474</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>23,1%</t>
+          <t>21,22%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>61,16%</t>
+          <t>60,31%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>3620</t>
+          <t>3641</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>11487</t>
+          <t>11123</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>15,33%</t>
+          <t>15,42%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>48,64%</t>
+          <t>47,1%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>8866</t>
+          <t>9237</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>18971</t>
+          <t>19539</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>21,63%</t>
+          <t>22,54%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>46,29%</t>
+          <t>47,68%</t>
         </is>
       </c>
     </row>
@@ -4853,12 +4853,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>6746</t>
+          <t>6894</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>13356</t>
+          <t>13683</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4868,12 +4868,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>38,84%</t>
+          <t>39,69%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>76,9%</t>
+          <t>78,78%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4888,12 +4888,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>12127</t>
+          <t>12491</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>19994</t>
+          <t>19973</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4903,12 +4903,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>51,36%</t>
+          <t>52,9%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>84,67%</t>
+          <t>84,58%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4923,12 +4923,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>22011</t>
+          <t>21443</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>32116</t>
+          <t>31745</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4938,12 +4938,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>53,71%</t>
+          <t>52,32%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>78,37%</t>
+          <t>77,46%</t>
         </is>
       </c>
     </row>
@@ -5088,7 +5088,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>4202</t>
+          <t>4241</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5103,7 +5103,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>85,15%</t>
+          <t>85,94%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>1235</t>
+          <t>1227</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>5220</t>
+          <t>5223</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>17,62%</t>
+          <t>17,5%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>74,49%</t>
+          <t>74,53%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>2677</t>
+          <t>2662</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>8211</t>
+          <t>8089</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>22,42%</t>
+          <t>22,29%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>68,75%</t>
+          <t>67,73%</t>
         </is>
       </c>
     </row>
@@ -5196,7 +5196,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>733</t>
+          <t>694</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -5211,7 +5211,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>14,85%</t>
+          <t>14,06%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -5231,12 +5231,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1788</t>
+          <t>1785</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>5773</t>
+          <t>5781</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5246,12 +5246,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>25,51%</t>
+          <t>25,47%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>82,38%</t>
+          <t>82,5%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5266,12 +5266,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>3733</t>
+          <t>3855</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>9267</t>
+          <t>9282</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5281,12 +5281,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>31,25%</t>
+          <t>32,27%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>77,58%</t>
+          <t>77,71%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>20707</t>
+          <t>20746</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>34466</t>
+          <t>34389</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>25,81%</t>
+          <t>25,86%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>42,97%</t>
+          <t>42,87%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>24362</t>
+          <t>23799</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>39458</t>
+          <t>38912</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>24,97%</t>
+          <t>24,39%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>40,44%</t>
+          <t>39,88%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>47937</t>
+          <t>49606</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>68617</t>
+          <t>69618</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>26,96%</t>
+          <t>27,9%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>38,59%</t>
+          <t>39,16%</t>
         </is>
       </c>
     </row>
@@ -5539,12 +5539,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>45752</t>
+          <t>45829</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>59511</t>
+          <t>59472</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5554,12 +5554,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>57,03%</t>
+          <t>57,13%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>74,19%</t>
+          <t>74,14%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5574,12 +5574,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>58120</t>
+          <t>58666</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>73216</t>
+          <t>73779</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5589,12 +5589,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>59,56%</t>
+          <t>60,12%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>75,03%</t>
+          <t>75,61%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5609,12 +5609,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>109179</t>
+          <t>108178</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>129859</t>
+          <t>128190</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5624,12 +5624,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>61,41%</t>
+          <t>60,84%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>73,04%</t>
+          <t>72,1%</t>
         </is>
       </c>
     </row>
@@ -6008,7 +6008,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>3147</t>
+          <t>2953</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6023,7 +6023,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>58,74%</t>
+          <t>55,11%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6038,12 +6038,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>2673</t>
+          <t>2572</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>6827</t>
+          <t>6239</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6053,12 +6053,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>35,75%</t>
+          <t>34,41%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>91,32%</t>
+          <t>83,45%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6073,12 +6073,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>2634</t>
+          <t>2864</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>8587</t>
+          <t>8590</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6088,12 +6088,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>20,52%</t>
+          <t>22,32%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>66,91%</t>
+          <t>66,93%</t>
         </is>
       </c>
     </row>
@@ -6116,7 +6116,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2211</t>
+          <t>2405</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -6131,7 +6131,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>41,26%</t>
+          <t>44,89%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -6151,12 +6151,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>1237</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>4803</t>
+          <t>4904</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6166,12 +6166,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>8,68%</t>
+          <t>16,55%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>64,25%</t>
+          <t>65,59%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6186,12 +6186,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>4247</t>
+          <t>4244</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>10200</t>
+          <t>9970</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6201,12 +6201,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>33,09%</t>
+          <t>33,07%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>79,48%</t>
+          <t>77,68%</t>
         </is>
       </c>
     </row>
@@ -6381,12 +6381,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2455</t>
+          <t>2290</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>6647</t>
+          <t>7099</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6396,12 +6396,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>28,77%</t>
+          <t>26,84%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>77,92%</t>
+          <t>83,21%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6416,12 +6416,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>4379</t>
+          <t>4465</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>9273</t>
+          <t>9727</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -6431,12 +6431,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>39,46%</t>
+          <t>40,23%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>83,55%</t>
+          <t>87,65%</t>
         </is>
       </c>
     </row>
@@ -6494,12 +6494,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1884</t>
+          <t>1432</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>6076</t>
+          <t>6241</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6509,12 +6509,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>22,08%</t>
+          <t>16,79%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>71,23%</t>
+          <t>73,16%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6529,12 +6529,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1825</t>
+          <t>1371</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>6719</t>
+          <t>6633</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6544,12 +6544,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>16,45%</t>
+          <t>12,35%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>60,54%</t>
+          <t>59,77%</t>
         </is>
       </c>
     </row>
@@ -6724,12 +6724,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>606</t>
+          <t>611</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>3929</t>
+          <t>4005</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6739,12 +6739,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>10,56%</t>
+          <t>10,64%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>68,4%</t>
+          <t>69,72%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6759,12 +6759,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>2002</t>
+          <t>1509</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>6631</t>
+          <t>6547</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6774,12 +6774,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>22,08%</t>
+          <t>16,64%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>73,14%</t>
+          <t>72,21%</t>
         </is>
       </c>
     </row>
@@ -6837,12 +6837,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>1815</t>
+          <t>1739</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>5138</t>
+          <t>5133</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6852,12 +6852,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>31,6%</t>
+          <t>30,28%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>89,44%</t>
+          <t>89,36%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6872,12 +6872,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>2436</t>
+          <t>2520</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>7065</t>
+          <t>7558</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6887,12 +6887,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>26,86%</t>
+          <t>27,79%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>77,92%</t>
+          <t>83,36%</t>
         </is>
       </c>
     </row>
@@ -7032,12 +7032,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1825</t>
+          <t>1920</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>7639</t>
+          <t>7885</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7047,12 +7047,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>11,12%</t>
+          <t>11,7%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>46,54%</t>
+          <t>48,05%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2063</t>
+          <t>1583</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>7315</t>
+          <t>7179</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7082,12 +7082,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>18,83%</t>
+          <t>14,45%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>66,79%</t>
+          <t>65,54%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7102,12 +7102,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>5074</t>
+          <t>5060</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>12948</t>
+          <t>12771</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7117,12 +7117,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>18,54%</t>
+          <t>18,49%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>47,32%</t>
+          <t>46,67%</t>
         </is>
       </c>
     </row>
@@ -7145,12 +7145,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>8773</t>
+          <t>8527</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>14587</t>
+          <t>14492</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7160,12 +7160,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>53,46%</t>
+          <t>51,95%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>88,88%</t>
+          <t>88,3%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7180,12 +7180,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3638</t>
+          <t>3774</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>8890</t>
+          <t>9370</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7195,12 +7195,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>33,21%</t>
+          <t>34,46%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>81,17%</t>
+          <t>85,55%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7215,12 +7215,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>14417</t>
+          <t>14594</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>22291</t>
+          <t>22305</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7230,12 +7230,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>52,68%</t>
+          <t>53,33%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>81,46%</t>
+          <t>81,51%</t>
         </is>
       </c>
     </row>
@@ -7375,12 +7375,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>4238</t>
+          <t>4268</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>10325</t>
+          <t>10159</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7390,12 +7390,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>30,82%</t>
+          <t>31,04%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>75,09%</t>
+          <t>73,89%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7410,12 +7410,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>700</t>
+          <t>709</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>5496</t>
+          <t>5268</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7425,12 +7425,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>7,06%</t>
+          <t>7,16%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>55,47%</t>
+          <t>53,16%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7445,12 +7445,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>5665</t>
+          <t>5779</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>13780</t>
+          <t>13832</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7460,12 +7460,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>23,95%</t>
+          <t>24,43%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>58,25%</t>
+          <t>58,47%</t>
         </is>
       </c>
     </row>
@@ -7488,12 +7488,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3424</t>
+          <t>3590</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>9511</t>
+          <t>9481</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7503,12 +7503,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>24,91%</t>
+          <t>26,11%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>69,18%</t>
+          <t>68,96%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7523,12 +7523,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>4413</t>
+          <t>4641</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>9209</t>
+          <t>9200</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7538,12 +7538,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>44,53%</t>
+          <t>46,84%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>92,94%</t>
+          <t>92,84%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7558,12 +7558,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>9878</t>
+          <t>9826</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>17993</t>
+          <t>17879</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7573,12 +7573,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>41,75%</t>
+          <t>41,53%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>76,05%</t>
+          <t>75,57%</t>
         </is>
       </c>
     </row>
@@ -7753,12 +7753,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>2195</t>
+          <t>2389</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>6507</t>
+          <t>6508</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7768,12 +7768,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>30,7%</t>
+          <t>33,41%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>91,0%</t>
+          <t>91,02%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7788,12 +7788,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>2949</t>
+          <t>3009</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>8015</t>
+          <t>8240</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7803,12 +7803,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>29,36%</t>
+          <t>29,95%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>79,78%</t>
+          <t>82,03%</t>
         </is>
       </c>
     </row>
@@ -7866,12 +7866,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>643</t>
+          <t>642</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>4955</t>
+          <t>4761</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7881,12 +7881,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>9,0%</t>
+          <t>8,98%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>69,3%</t>
+          <t>66,59%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7901,12 +7901,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>2031</t>
+          <t>1806</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>7097</t>
+          <t>7037</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7916,12 +7916,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>20,22%</t>
+          <t>17,97%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>70,64%</t>
+          <t>70,05%</t>
         </is>
       </c>
     </row>
@@ -8061,12 +8061,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>12799</t>
+          <t>13194</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>23747</t>
+          <t>23476</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8076,12 +8076,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>28,89%</t>
+          <t>29,78%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>53,6%</t>
+          <t>52,99%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8096,12 +8096,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>17712</t>
+          <t>17651</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>29016</t>
+          <t>29365</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8111,12 +8111,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>35,59%</t>
+          <t>35,47%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>58,31%</t>
+          <t>59,01%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8131,12 +8131,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>34095</t>
+          <t>33380</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>49534</t>
+          <t>48963</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8146,12 +8146,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>36,25%</t>
+          <t>35,48%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>52,66%</t>
+          <t>52,05%</t>
         </is>
       </c>
     </row>
@@ -8174,12 +8174,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>20557</t>
+          <t>20828</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>31505</t>
+          <t>31110</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8189,12 +8189,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>46,4%</t>
+          <t>47,01%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>71,11%</t>
+          <t>70,22%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8209,12 +8209,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>20748</t>
+          <t>20399</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>32052</t>
+          <t>32113</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8224,12 +8224,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>41,69%</t>
+          <t>40,99%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>64,41%</t>
+          <t>64,53%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8244,12 +8244,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>44534</t>
+          <t>45105</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>59973</t>
+          <t>60688</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8259,12 +8259,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>47,34%</t>
+          <t>47,95%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>63,75%</t>
+          <t>64,52%</t>
         </is>
       </c>
     </row>
@@ -8638,12 +8638,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>2349</t>
+          <t>2376</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>7376</t>
+          <t>7740</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -8653,12 +8653,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>22,11%</t>
+          <t>22,37%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>69,43%</t>
+          <t>72,86%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8673,12 +8673,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>863</t>
+          <t>828</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>6794</t>
+          <t>6418</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -8688,12 +8688,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>6,05%</t>
+          <t>5,81%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>47,63%</t>
+          <t>44,99%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8708,12 +8708,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>4669</t>
+          <t>4654</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>12115</t>
+          <t>12542</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -8723,12 +8723,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>18,76%</t>
+          <t>18,7%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>48,68%</t>
+          <t>50,39%</t>
         </is>
       </c>
     </row>
@@ -8751,12 +8751,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>3247</t>
+          <t>2883</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>8274</t>
+          <t>8247</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -8766,12 +8766,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>30,57%</t>
+          <t>27,14%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>77,89%</t>
+          <t>77,63%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8786,12 +8786,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>7470</t>
+          <t>7846</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>13401</t>
+          <t>13436</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -8801,12 +8801,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>52,37%</t>
+          <t>55,01%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>93,95%</t>
+          <t>94,19%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8821,12 +8821,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>12773</t>
+          <t>12346</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>20219</t>
+          <t>20234</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -8836,12 +8836,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>51,32%</t>
+          <t>49,61%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>81,24%</t>
+          <t>81,3%</t>
         </is>
       </c>
     </row>
@@ -8981,12 +8981,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>720</t>
+          <t>749</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>4860</t>
+          <t>4877</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -8996,12 +8996,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>8,78%</t>
+          <t>9,14%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>59,26%</t>
+          <t>59,47%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -9016,12 +9016,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1165</t>
+          <t>890</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>7516</t>
+          <t>7065</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -9031,12 +9031,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>10,37%</t>
+          <t>7,92%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>66,85%</t>
+          <t>62,85%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -9051,12 +9051,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>2717</t>
+          <t>2543</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>10248</t>
+          <t>9990</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -9066,12 +9066,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>13,97%</t>
+          <t>13,08%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>52,71%</t>
+          <t>51,38%</t>
         </is>
       </c>
     </row>
@@ -9094,12 +9094,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>3341</t>
+          <t>3324</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>7481</t>
+          <t>7452</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -9109,12 +9109,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>40,74%</t>
+          <t>40,53%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>91,22%</t>
+          <t>90,86%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -9129,12 +9129,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>3726</t>
+          <t>4177</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>10077</t>
+          <t>10352</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -9144,12 +9144,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>33,15%</t>
+          <t>37,15%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>89,63%</t>
+          <t>92,08%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -9164,12 +9164,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>9196</t>
+          <t>9454</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>16727</t>
+          <t>16901</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -9179,12 +9179,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>47,29%</t>
+          <t>48,62%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>86,03%</t>
+          <t>86,92%</t>
         </is>
       </c>
     </row>
@@ -9359,12 +9359,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>532</t>
+          <t>522</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>5041</t>
+          <t>4695</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -9374,12 +9374,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>6,85%</t>
+          <t>6,72%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>64,9%</t>
+          <t>60,44%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -9394,12 +9394,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>871</t>
+          <t>1037</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>5757</t>
+          <t>6057</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -9409,12 +9409,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>8,43%</t>
+          <t>10,04%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>55,74%</t>
+          <t>58,64%</t>
         </is>
       </c>
     </row>
@@ -9472,12 +9472,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>2727</t>
+          <t>3073</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>7236</t>
+          <t>7246</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -9487,12 +9487,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>35,1%</t>
+          <t>39,56%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>93,15%</t>
+          <t>93,28%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -9507,12 +9507,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>4572</t>
+          <t>4272</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>9458</t>
+          <t>9292</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -9522,12 +9522,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>44,26%</t>
+          <t>41,36%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>91,57%</t>
+          <t>89,96%</t>
         </is>
       </c>
     </row>
@@ -9667,12 +9667,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3399</t>
+          <t>3215</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>18493</t>
+          <t>18123</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -9682,12 +9682,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>14,0%</t>
+          <t>13,24%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>76,14%</t>
+          <t>74,62%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9702,12 +9702,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>4033</t>
+          <t>4108</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>12569</t>
+          <t>12175</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -9717,12 +9717,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>12,91%</t>
+          <t>13,16%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>40,25%</t>
+          <t>38,99%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9737,12 +9737,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>9956</t>
+          <t>10187</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>30330</t>
+          <t>30514</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -9752,12 +9752,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>17,93%</t>
+          <t>18,35%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>54,63%</t>
+          <t>54,96%</t>
         </is>
       </c>
     </row>
@@ -9780,12 +9780,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>5796</t>
+          <t>6166</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>20890</t>
+          <t>21074</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -9795,12 +9795,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>23,86%</t>
+          <t>25,38%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>86,0%</t>
+          <t>86,76%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9815,12 +9815,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>18659</t>
+          <t>19053</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>27195</t>
+          <t>27120</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -9830,12 +9830,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>59,75%</t>
+          <t>61,01%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>87,09%</t>
+          <t>86,84%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9850,12 +9850,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>25187</t>
+          <t>25003</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>45561</t>
+          <t>45330</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -9865,12 +9865,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>45,37%</t>
+          <t>45,04%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>82,07%</t>
+          <t>81,65%</t>
         </is>
       </c>
     </row>
@@ -10010,12 +10010,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1272</t>
+          <t>1079</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>6711</t>
+          <t>6631</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -10025,12 +10025,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>9,77%</t>
+          <t>8,29%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>51,55%</t>
+          <t>50,93%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -10045,12 +10045,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1615</t>
+          <t>1743</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>15207</t>
+          <t>14886</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -10060,12 +10060,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>6,1%</t>
+          <t>6,58%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>57,39%</t>
+          <t>56,18%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -10080,12 +10080,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>3808</t>
+          <t>4258</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>18005</t>
+          <t>18827</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -10095,12 +10095,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>9,64%</t>
+          <t>10,78%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>45,56%</t>
+          <t>47,65%</t>
         </is>
       </c>
     </row>
@@ -10123,12 +10123,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>6309</t>
+          <t>6389</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>11748</t>
+          <t>11941</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -10138,12 +10138,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>48,45%</t>
+          <t>49,07%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>90,23%</t>
+          <t>91,71%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -10158,12 +10158,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>11289</t>
+          <t>11610</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>24881</t>
+          <t>24753</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -10173,12 +10173,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>42,61%</t>
+          <t>43,82%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>93,9%</t>
+          <t>93,42%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -10193,12 +10193,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>21510</t>
+          <t>20688</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>35707</t>
+          <t>35257</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -10208,12 +10208,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>54,44%</t>
+          <t>52,35%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>90,36%</t>
+          <t>89,22%</t>
         </is>
       </c>
     </row>
@@ -10353,7 +10353,7 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>804</t>
+          <t>737</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
@@ -10368,7 +10368,7 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>19,65%</t>
+          <t>18,03%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
@@ -10388,7 +10388,7 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>1882</t>
+          <t>1965</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
@@ -10403,7 +10403,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>33,38%</t>
+          <t>34,83%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -10423,12 +10423,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>4017</t>
+          <t>3887</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>8861</t>
+          <t>8911</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -10438,12 +10438,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>41,29%</t>
+          <t>39,96%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>91,08%</t>
+          <t>91,59%</t>
         </is>
       </c>
     </row>
@@ -10471,7 +10471,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>3284</t>
+          <t>3394</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -10486,7 +10486,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>80,31%</t>
+          <t>83,01%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -10506,7 +10506,7 @@
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>3754</t>
+          <t>3676</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -10521,7 +10521,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>66,56%</t>
+          <t>65,18%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -10536,12 +10536,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>868</t>
+          <t>818</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>5712</t>
+          <t>5842</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -10551,12 +10551,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>8,92%</t>
+          <t>8,41%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>58,71%</t>
+          <t>60,04%</t>
         </is>
       </c>
     </row>
@@ -10696,12 +10696,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>17385</t>
+          <t>17052</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>37000</t>
+          <t>35165</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -10711,12 +10711,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>27,69%</t>
+          <t>27,16%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>58,93%</t>
+          <t>56,01%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10731,12 +10731,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>17162</t>
+          <t>18594</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>37214</t>
+          <t>37314</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -10746,12 +10746,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>17,76%</t>
+          <t>19,24%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>38,51%</t>
+          <t>38,61%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10766,12 +10766,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>39090</t>
+          <t>39814</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>65894</t>
+          <t>67883</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -10781,12 +10781,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>24,52%</t>
+          <t>24,97%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>41,33%</t>
+          <t>42,58%</t>
         </is>
       </c>
     </row>
@@ -10809,12 +10809,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>25782</t>
+          <t>27617</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>45397</t>
+          <t>45730</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -10824,12 +10824,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>41,07%</t>
+          <t>43,99%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>72,31%</t>
+          <t>72,84%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -10844,12 +10844,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>59425</t>
+          <t>59325</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>79477</t>
+          <t>78045</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -10859,12 +10859,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>61,49%</t>
+          <t>61,39%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>82,24%</t>
+          <t>80,76%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -10879,12 +10879,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>93527</t>
+          <t>91538</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>120331</t>
+          <t>119607</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -10894,12 +10894,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>58,67%</t>
+          <t>57,42%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>75,48%</t>
+          <t>75,03%</t>
         </is>
       </c>
     </row>
